--- a/space-battleship/config_excel/crew_level.xlsx
+++ b/space-battleship/config_excel/crew_level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crew_level" sheetId="1" r:id="R56265ea8af58442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="crew_level" sheetId="1" r:id="R8fa9cba23f19491f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -357,7 +357,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="7" t="n">
-        <x:v>200</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D6" s="7" t="n">
         <x:v>1.2</x:v>
